--- a/results/auto_Cape_Town_Senior_Care.xlsx
+++ b/results/auto_Cape_Town_Senior_Care.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>info@maitlandcottage.co.za</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -492,9 +489,6 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -509,9 +503,6 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -526,9 +517,6 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -543,9 +531,6 @@
       <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -560,9 +545,6 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -577,9 +559,6 @@
       <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -594,9 +573,6 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -611,9 +587,6 @@
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -628,9 +601,6 @@
       <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -644,9 +614,6 @@
       </c>
       <c r="D11" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7">

--- a/results/auto_Cape_Town_Senior_Care.xlsx
+++ b/results/auto_Cape_Town_Senior_Care.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>info@maitlandcottage.co.za</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -489,6 +492,9 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -503,6 +509,9 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -517,6 +526,9 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -531,6 +543,9 @@
       <c r="D5" t="s">
         <v>25</v>
       </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -545,6 +560,9 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -559,6 +577,9 @@
       <c r="D7" t="s">
         <v>27</v>
       </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -573,6 +594,9 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -587,6 +611,9 @@
       <c r="D9" t="s">
         <v>29</v>
       </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -601,6 +628,9 @@
       <c r="D10" t="s">
         <v>30</v>
       </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -615,6 +645,9 @@
       <c r="D11" t="s">
         <v>31</v>
       </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -629,6 +662,9 @@
       <c r="D12" t="s">
         <v>32</v>
       </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
@@ -643,6 +679,9 @@
       <c r="D13" t="s">
         <v>33</v>
       </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
@@ -656,6 +695,9 @@
       </c>
       <c r="D14" t="s">
         <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
